--- a/output/pdf_financials_xlsx/SAT.xlsx
+++ b/output/pdf_financials_xlsx/SAT.xlsx
@@ -5868,13 +5868,13 @@
         <v>-0.679526</v>
       </c>
       <c r="E124" s="3" t="n">
-        <v>-0.679522</v>
+        <v>-0.879522</v>
       </c>
       <c r="F124" s="3" t="n">
         <v>-0.679514</v>
       </c>
       <c r="G124" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H124" s="3" t="n">
         <v>0</v>
@@ -5911,13 +5911,13 @@
         <v>-0.679526</v>
       </c>
       <c r="E125" s="3" t="n">
-        <v>-0.679522</v>
+        <v>-0.879522</v>
       </c>
       <c r="F125" s="3" t="n">
         <v>-0.679514</v>
       </c>
       <c r="G125" s="3" t="n">
-        <v>0</v>
+        <v>0.23</v>
       </c>
       <c r="H125" s="3" t="n">
         <v>0</v>
@@ -8808,7 +8808,7 @@
       </c>
       <c r="D33" t="inlineStr">
         <is>
-          <t>Cash</t>
+          <t>CashAndCashEquivalents</t>
         </is>
       </c>
       <c r="E33" t="inlineStr">
@@ -19670,7 +19670,11 @@
           <t>Repayment of bank indebtedness</t>
         </is>
       </c>
-      <c r="D181" t="inlineStr"/>
+      <c r="D181" t="inlineStr">
+        <is>
+          <t>RepaymentOfDebt</t>
+        </is>
+      </c>
       <c r="E181" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/SAT.xlsx
+++ b/output/pdf_financials_xlsx/SAT.xlsx
@@ -1138,10 +1138,10 @@
         <v>-0.219677</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>-1.501713</v>
+        <v>-2.032415</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>-2.329177</v>
+        <v>-2.723382</v>
       </c>
       <c r="I16" s="3" t="n">
         <v>-0.323657</v>
@@ -1181,10 +1181,10 @@
         <v>0.055648</v>
       </c>
       <c r="G17" s="3" t="n">
-        <v>-0</v>
+        <v>0.530702</v>
       </c>
       <c r="H17" s="3" t="n">
-        <v>-0</v>
+        <v>0.394205</v>
       </c>
       <c r="I17" s="3" t="n">
         <v>0.156772</v>
@@ -1663,10 +1663,10 @@
         <v>-0.219677</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>-1.501713</v>
+        <v>-2.032415</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>-2.329177</v>
+        <v>-2.723382</v>
       </c>
       <c r="I27" s="3" t="n">
         <v>-0.323657</v>
@@ -1749,10 +1749,10 @@
         <v>0.286085</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>-1.016641</v>
+        <v>-1.547343</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>-1.445499</v>
+        <v>-1.839704</v>
       </c>
       <c r="I29" s="3" t="n">
         <v>0.5317190000000001</v>
@@ -1859,10 +1859,10 @@
         <v>-25.33173705030568</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>-0</v>
+        <v>-26.11189151821847</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>-0</v>
+        <v>-14.47483313027699</v>
       </c>
       <c r="I31" s="3" t="n">
         <v>-48.43769793330594</v>
@@ -3422,22 +3422,22 @@
         <v>0</v>
       </c>
       <c r="H67" s="3" t="n">
-        <v>0</v>
+        <v>1.22829</v>
       </c>
       <c r="I67" s="3" t="n">
-        <v>0</v>
+        <v>0.187625</v>
       </c>
       <c r="J67" s="3" t="n">
-        <v>0</v>
+        <v>0.48669</v>
       </c>
       <c r="K67" s="3" t="n">
-        <v>0</v>
+        <v>0.604097</v>
       </c>
       <c r="L67" s="3" t="n">
-        <v>0</v>
+        <v>0.307119</v>
       </c>
       <c r="M67" s="3" t="n">
-        <v>0</v>
+        <v>0.070228</v>
       </c>
     </row>
     <row r="68">
@@ -24400,7 +24400,11 @@
           <t>Income tax recovery 8</t>
         </is>
       </c>
-      <c r="D246" t="inlineStr"/>
+      <c r="D246" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E246" t="inlineStr">
         <is>
           <t>-</t>
@@ -24978,7 +24982,11 @@
           <t>Income tax (recovery) expense 8</t>
         </is>
       </c>
-      <c r="D254" t="inlineStr"/>
+      <c r="D254" t="inlineStr">
+        <is>
+          <t>TaxProvision</t>
+        </is>
+      </c>
       <c r="E254" t="inlineStr">
         <is>
           <t>-</t>
